--- a/ECPRM2.xlsx
+++ b/ECPRM2.xlsx
@@ -37,7 +37,7 @@
     <t>20008081</t>
   </si>
   <si>
-    <t>PEDIASURE MDU.KLG800</t>
+    <t>PDIASURE M KLG 800 G</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
@@ -55,7 +55,7 @@
     <t>10025849</t>
   </si>
   <si>
-    <t>NTRILON RYL3 VAN 800</t>
+    <t>NTRILON RYL3 V 800 G</t>
   </si>
   <si>
     <t>4</t>
@@ -64,7 +64,7 @@
     <t>10004532</t>
   </si>
   <si>
-    <t>ENSURE/G VANILLA 800</t>
+    <t>ENSURE/G VAN 800 G</t>
   </si>
   <si>
     <t>5</t>
